--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484119_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484119_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6953</v>
+        <v>8.6302</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5471</v>
+        <v>7.0993</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1481</v>
+        <v>1.5309</v>
       </c>
       <c r="G2" t="n">
         <v>0.1724</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3715</v>
+        <v>1.3065</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1791</v>
+        <v>0.7313</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1924</v>
+        <v>0.5752</v>
       </c>
       <c r="V2" t="n">
         <v>5.961</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7666</v>
+        <v>6.4258</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7247</v>
+        <v>6.9911</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-0.5654</v>
       </c>
       <c r="G3" t="n">
         <v>5.8528</v>
@@ -688,13 +688,13 @@
         <v>2.7774</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2766</v>
+        <v>0.3826</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6236</v>
+        <v>0.89</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9002</v>
+        <v>-0.5074</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6032</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1152</v>
+        <v>2.8091</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4386</v>
+        <v>3.1325</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3233</v>
@@ -766,10 +766,10 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>1.026</v>
+        <v>0.7199</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8106</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="U4" t="n">
         <v>0.2153</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.626</v>
+        <v>2.8006</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9406</v>
+        <v>1.0029</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6855</v>
+        <v>1.7977</v>
       </c>
       <c r="G5" t="n">
         <v>1.7411</v>
@@ -844,13 +844,13 @@
         <v>2.7774</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1746</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4876</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6621</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8883</v>
+        <v>1.7481</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8406</v>
+        <v>3.2638</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0477</v>
+        <v>-1.5157</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1654</v>
+        <v>-0.3661</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1615</v>
+        <v>-0.3882</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0039</v>
+        <v>0.0221</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3985</v>
+        <v>3.0994</v>
       </c>
       <c r="K6" t="n">
-        <v>0.278</v>
+        <v>0.4085</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1205</v>
+        <v>2.6908</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.233</v>
+        <v>-3.4655</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1165</v>
+        <v>-0.7967</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1165</v>
+        <v>-2.6688</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>1.731</v>
+        <v>0.1304</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4422</v>
+        <v>0.1644</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2888</v>
+        <v>-0.034</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9058</v>
+        <v>1.5375</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6555</v>
+        <v>1.107</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5613</v>
+        <v>0.4305</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1654</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.683</v>
+        <v>0.1615</v>
       </c>
       <c r="I7" t="n">
-        <v>1.753</v>
+        <v>0.0039</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5116</v>
+        <v>0.3985</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6321</v>
+        <v>0.278</v>
       </c>
       <c r="L7" t="n">
         <v>0.1205</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5815</v>
+        <v>-0.233</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0509</v>
+        <v>-0.1165</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6325</v>
+        <v>-0.1165</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1018</v>
+        <v>1.3801</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8399</v>
+        <v>0.7086</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7381</v>
+        <v>0.6716</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8692</v>
+        <v>-0.6032</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8692</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8095</v>
+        <v>1.2727</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5496</v>
+        <v>1.347</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7401</v>
+        <v>-0.0743</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3661</v>
+        <v>-0.8075</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3882</v>
+        <v>0.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0221</v>
+        <v>-0.9342</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0994</v>
+        <v>2.3729</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4085</v>
+        <v>1.7201</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6908</v>
+        <v>0.6528</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.4655</v>
+        <v>-3.1803</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7967</v>
+        <v>-1.5934</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.6688</v>
+        <v>-1.587</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9838</v>
+        <v>2.7774</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9838</v>
+        <v>3.7693</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8082</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5498</v>
+        <v>-0.0339</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2585</v>
+        <v>-0.6632</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4656</v>
+        <v>-0.496</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8766</v>
+        <v>-2.2257</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.411</v>
+        <v>1.7297</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1267</v>
+        <v>-1.683</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9342</v>
+        <v>1.753</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3729</v>
+        <v>-1.5116</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7201</v>
+        <v>-1.6321</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6528</v>
+        <v>0.1205</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1803</v>
+        <v>1.5815</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5934</v>
+        <v>-0.0509</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.587</v>
+        <v>1.6325</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7774</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7693</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5043</v>
+        <v>0.7</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5044</v>
+        <v>1.2697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9999</v>
+        <v>-0.5697</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7564</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1467</v>
+        <v>-0.0844</v>
       </c>
       <c r="F10" t="n">
         <v>-0.6097</v>
@@ -1234,10 +1234,10 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.187</v>
+        <v>-0.1247</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.187</v>
+        <v>-0.1247</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6511</v>
+        <v>-1.1265</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5493</v>
+        <v>-3.2352</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1018</v>
+        <v>2.1086</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8983</v>
+        <v>-0.8512</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1362</v>
+        <v>-2.0665</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.762</v>
+        <v>1.2153</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2999</v>
+        <v>-1.6983</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0605</v>
+        <v>-1.8188</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3604</v>
+        <v>0.1205</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5983000000000001</v>
+        <v>0.8472</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1967</v>
+        <v>-0.2477</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4016</v>
+        <v>1.0948</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5952</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.348</v>
+        <v>-0.2239</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2494</v>
+        <v>0.2325</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.4564</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1134</v>
+        <v>-1.5327</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2781</v>
+        <v>-1.4869</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1647</v>
+        <v>-0.0457</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8512</v>
+        <v>-1.8983</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0665</v>
+        <v>-0.1362</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2153</v>
+        <v>-1.762</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6983</v>
+        <v>-1.2999</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8188</v>
+        <v>0.0605</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1205</v>
+        <v>-1.3604</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8472</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2477</v>
+        <v>-0.1967</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0948</v>
+        <v>-0.4016</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2108</v>
+        <v>-0.2296</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8105</v>
+        <v>-0.187</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4003</v>
+        <v>-0.0425</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.7514</v>
+        <v>21.3747</v>
       </c>
       <c r="E13" t="n">
-        <v>16.2882</v>
+        <v>16.9114</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4632</v>
+        <v>4.4633</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9916</v>
+        <v>3.991600000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-2.7452</v>
       </c>
       <c r="I13" t="n">
-        <v>6.737000000000001</v>
+        <v>6.737</v>
       </c>
       <c r="J13" t="n">
         <v>17.7392</v>
       </c>
       <c r="K13" t="n">
-        <v>3.132200000000001</v>
+        <v>3.1322</v>
       </c>
       <c r="L13" t="n">
         <v>14.6067</v>
@@ -1468,13 +1468,13 @@
         <v>20.83039999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7208</v>
+        <v>3.3442</v>
       </c>
       <c r="T13" t="n">
-        <v>4.081900000000001</v>
+        <v>4.705299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3612</v>
+        <v>-1.361</v>
       </c>
       <c r="V13" t="n">
         <v>6.1037</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5612</v>
+        <v>0.9065</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4698</v>
+        <v>1.3535</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9087</v>
+        <v>-0.447</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1488</v>
+        <v>-0.7377</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8824</v>
+        <v>1.0981</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0312</v>
+        <v>-1.8358</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2907</v>
+        <v>1.1446</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1301</v>
+        <v>0.4542</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1606</v>
+        <v>0.6904</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4395</v>
+        <v>-1.8823</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2477</v>
+        <v>0.6439</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1918</v>
+        <v>-2.5262</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1822</v>
+        <v>-1.3887</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S14" t="n">
-        <v>3.287</v>
+        <v>-0.3557</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3613</v>
+        <v>0.3912</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0743</v>
+        <v>-0.7469</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5852000000000001</v>
+        <v>1.2065</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5852000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0486</v>
+        <v>-0.1912</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4353</v>
+        <v>0.6333</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3867</v>
+        <v>-0.8245</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7377</v>
+        <v>-0.1488</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0981</v>
+        <v>0.8824</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8358</v>
+        <v>-1.0312</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1446</v>
+        <v>1.2907</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4542</v>
+        <v>1.1301</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6904</v>
+        <v>0.1606</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8823</v>
+        <v>-1.4395</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6439</v>
+        <v>-0.2477</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5262</v>
+        <v>-1.1918</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7935</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3887</v>
+        <v>-2.1822</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2136</v>
+        <v>1.5346</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5271</v>
+        <v>1.5248</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6866</v>
+        <v>0.0098</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2065</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5852000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>D. GUILLEN VIVES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2774</v>
+        <v>-0.2669</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4389</v>
+        <v>0.518</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7163</v>
+        <v>-0.7849</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9241</v>
+        <v>-0.1443</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0612</v>
+        <v>-0.7156</v>
       </c>
       <c r="I16" t="n">
-        <v>1.863</v>
+        <v>0.5713</v>
       </c>
       <c r="J16" t="n">
-        <v>6.9538</v>
+        <v>0.8524</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8909</v>
+        <v>0.2876</v>
       </c>
       <c r="L16" t="n">
-        <v>5.0629</v>
+        <v>0.5648</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0297</v>
+        <v>-0.9967</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1702</v>
+        <v>-1.0032</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.1999</v>
+        <v>0.0065</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.1741</v>
+        <v>0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.158</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>0.1984</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5281</v>
+        <v>-0.2678</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3888</v>
+        <v>-0.3344</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1393</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.5555</v>
+        <v>-0.0532</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7458</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8097</v>
+        <v>-0.0532</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GUILLEN VIVES</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4531</v>
+        <v>-0.7123</v>
       </c>
       <c r="E17" t="n">
-        <v>0.416</v>
+        <v>-0.6698</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8691</v>
+        <v>-0.0425</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1443</v>
+        <v>0.2484</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7156</v>
+        <v>0.514</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5713</v>
+        <v>-0.2656</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8524</v>
+        <v>0.6452</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2876</v>
+        <v>0.6452</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5648</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9967</v>
+        <v>-0.3967</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0032</v>
+        <v>-0.1312</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0065</v>
+        <v>-0.2656</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.454</v>
+        <v>-0.1672</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4364</v>
+        <v>-0.1247</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0176</v>
+        <v>-0.0425</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0532</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>M. GONZALEZ DE UBIETA BELLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7684</v>
+        <v>-1.3052</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6698</v>
+        <v>0.4824</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-1.7876</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2484</v>
+        <v>-0.9821</v>
       </c>
       <c r="H18" t="n">
-        <v>0.514</v>
+        <v>1.8642</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2656</v>
+        <v>-2.8464</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6452</v>
+        <v>1.4345</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6452</v>
+        <v>2.0268</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3967</v>
+        <v>-2.4167</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1312</v>
+        <v>-0.1625</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2656</v>
+        <v>-2.2542</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1903</v>
+        <v>-1.3887</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3968</v>
+        <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2233</v>
+        <v>-0.1941</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1247</v>
+        <v>0.4366</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.6307</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9224</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.9224</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2628</v>
+        <v>-1.3546</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5473</v>
+        <v>0.3433</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8101</v>
+        <v>-1.6979</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1028</v>
@@ -1936,13 +1936,13 @@
         <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5486</v>
+        <v>-0.6405</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1304</v>
+        <v>-0.0736</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6791</v>
+        <v>-0.5669</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2065</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9142</v>
+        <v>-1.4626</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.67</v>
+        <v>1.6227</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2442</v>
+        <v>-3.0852</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4828</v>
+        <v>3.9241</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0458</v>
+        <v>2.0612</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5286</v>
+        <v>1.863</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3911</v>
+        <v>6.9538</v>
       </c>
       <c r="K20" t="n">
-        <v>0.746</v>
+        <v>1.8909</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6451</v>
+        <v>5.0629</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9083</v>
+        <v>-3.0297</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.1702</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1165</v>
+        <v>-3.1999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1822</v>
+        <v>-5.158</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0146</v>
+        <v>0.3429</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7481</v>
+        <v>0.5726</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2665</v>
+        <v>-0.2297</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3904</v>
+        <v>-2.5555</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8692</v>
+        <v>-0.7458</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2597</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9784</v>
+        <v>-1.6536</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2774</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.701</v>
+        <v>-0.6823</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3817</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5515</v>
+        <v>-0.2267</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0527</v>
+        <v>-0.034</v>
       </c>
       <c r="V21" t="n">
         <v>0.55</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. GONZALEZ DE UBIETA BELLO</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2701</v>
+        <v>-1.8122</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0743</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3444</v>
+        <v>-1.2442</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9821</v>
+        <v>0.4828</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8642</v>
+        <v>-0.0458</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8464</v>
+        <v>0.5286</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4345</v>
+        <v>1.3911</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0268</v>
+        <v>0.746</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.6451</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4167</v>
+        <v>-0.9083</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1625</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2542</v>
+        <v>-0.1165</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7935</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3887</v>
+        <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1591</v>
+        <v>-0.9126</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0284</v>
+        <v>-0.6461</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1876</v>
+        <v>-0.2665</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9224</v>
+        <v>-0.3904</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9224</v>
+        <v>-1.2597</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1509</v>
+        <v>-3.0149</v>
       </c>
       <c r="E23" t="n">
         <v>-0.9826</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1684</v>
+        <v>-2.0323</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7428</v>
@@ -2248,13 +2248,13 @@
         <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.6688</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4364</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3685</v>
+        <v>-0.2324</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4121</v>
+        <v>-3.8739</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5115</v>
+        <v>-2.0013</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9006</v>
+        <v>-1.8725</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5712</v>
@@ -2326,13 +2326,13 @@
         <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7975</v>
+        <v>-0.2593</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4874</v>
+        <v>0.0227</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3101</v>
+        <v>-0.2821</v>
       </c>
       <c r="V24" t="n">
         <v>-0.266</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8738</v>
+        <v>-5.2838</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7336</v>
+        <v>-4.2235</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1402</v>
+        <v>-1.0603</v>
       </c>
       <c r="G25" t="n">
         <v>-3.8356</v>
@@ -2404,13 +2404,13 @@
         <v>0.5952</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.1785</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.289</v>
+        <v>0.2211</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4796</v>
+        <v>-0.3996</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6745</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-20.7514</v>
+        <v>-20.0247</v>
       </c>
       <c r="E26" t="n">
         <v>-4.4633</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.2883</v>
+        <v>-15.5612</v>
       </c>
       <c r="G26" t="n">
         <v>-3.9917</v>
       </c>
       <c r="H26" t="n">
-        <v>2.745200000000001</v>
+        <v>2.7452</v>
       </c>
       <c r="I26" t="n">
         <v>-6.7369</v>
@@ -2482,13 +2482,13 @@
         <v>12.895</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.7206</v>
+        <v>-1.9937</v>
       </c>
       <c r="T26" t="n">
-        <v>1.361</v>
+        <v>1.3611</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.0819</v>
+        <v>-3.3549</v>
       </c>
       <c r="V26" t="n">
         <v>-6.1037</v>
@@ -2497,7 +2497,7 @@
         <v>1.2586</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.3624</v>
+        <v>-7.362399999999999</v>
       </c>
     </row>
   </sheetData>
